--- a/Supplementary_Information/S5_Table_Signal_Detection_Thresholds.xlsx
+++ b/Supplementary_Information/S5_Table_Signal_Detection_Thresholds.xlsx
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -136,6 +136,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -650,6 +653,28 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Drug role</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Primary suspect (FAERS role code PS) only</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>This study</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Secondary suspect, concomitant and interacting drugs are not counted in the 2x2 table</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
